--- a/sample_data/projects/hr_003/engagement_workbook.xlsx
+++ b/sample_data/projects/hr_003/engagement_workbook.xlsx
@@ -502,24 +502,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Approve JE, Create PO, Post JE</t>
+          <t>Approve Access, Create Vendor, Maintain Access</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>CC-427: Manager review of transactions</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -534,12 +530,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Process Payment</t>
+          <t>Create Vendor</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -567,7 +563,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Approve PO, Process Payment</t>
+          <t>Approve JE, Approve Access</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -590,12 +586,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Approve JE, Create PO</t>
+          <t>Approve PO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -618,20 +614,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Approve JE</t>
+          <t>Create Vendor, Process Payment, Post JE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CC-193: Manager review of transactions</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -646,24 +646,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Post JE, Approve JE</t>
+          <t>Approve PO, Create Vendor, Maintain Access</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>CC-844: Manager review of transactions</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -683,12 +679,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Approve JE, Post JE</t>
+          <t>Post JE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -711,7 +707,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Process Payment</t>
+          <t>Approve PO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -734,12 +730,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Maintain Access</t>
+          <t>Approve Access</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -762,12 +758,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Approve JE</t>
+          <t>Approve Access, Create PO, Approve JE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -790,12 +786,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Create PO, Maintain Access</t>
+          <t>Approve JE, Approve Access, Create PO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -823,19 +819,15 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Post JE, Create PO, Approve PO</t>
+          <t>Create Vendor, Approve JE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>CC-926: Manager review of transactions</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -855,7 +847,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Approve Access, Create PO</t>
+          <t>Process Payment, Create PO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -878,12 +870,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Post JE, Create PO, Maintain Access</t>
+          <t>Process Payment</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -906,12 +898,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Maintain Access, Approve JE, Create Vendor</t>
+          <t>Approve JE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -934,24 +926,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Approve PO, Post JE, Create PO</t>
+          <t>Create Vendor, Post JE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>CC-168: Manager review of transactions</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -966,12 +954,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Maintain Access, Create PO, Post JE</t>
+          <t>Post JE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -994,12 +982,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Create Vendor, Approve PO</t>
+          <t>Approve Access, Post JE, Process Payment</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1022,12 +1010,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Approve JE, Maintain Access</t>
+          <t>Approve PO, Approve Access, Create Vendor</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1055,19 +1043,15 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Approve JE, Create Vendor, Process Payment</t>
+          <t>Approve Access, Approve JE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>CC-189: Manager review of transactions</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1087,7 +1071,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Approve PO</t>
+          <t>Create Vendor</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1110,12 +1094,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Approve PO</t>
+          <t>Create PO, Maintain Access</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1138,12 +1122,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Create Vendor</t>
+          <t>Create Vendor, Approve Access, Approve PO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1166,20 +1150,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Approve JE, Process Payment</t>
+          <t>Process Payment, Create Vendor</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>CC-622: Manager review of transactions</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1194,12 +1182,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Approve JE, Maintain Access, Approve PO</t>
+          <t>Post JE</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1222,17 +1210,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Approve Access, Create Vendor</t>
+          <t>Post JE, Approve PO, Approve JE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1250,20 +1238,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Create Vendor</t>
+          <t>Approve PO, Post JE, Approve JE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>CC-556: Manager review of transactions</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1278,24 +1270,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Create PO, Approve PO, Create Vendor</t>
+          <t>Create Vendor, Approve PO, Approve JE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>CC-497: Manager review of transactions</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1310,12 +1298,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Process Payment</t>
+          <t>Create PO, Maintain Access, Approve Access</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1338,12 +1326,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Create PO, Approve JE</t>
+          <t>Post JE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1366,20 +1354,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Create Vendor, Create PO</t>
+          <t>Maintain Access, Post JE, Approve JE</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>CC-928: Manager review of transactions</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1394,20 +1386,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Process Payment, Create PO</t>
+          <t>Post JE, Approve JE</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>CC-156: Manager review of transactions</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1422,12 +1418,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Create Vendor</t>
+          <t>Process Payment, Maintain Access</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1450,12 +1446,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Create PO</t>
+          <t>Approve Access, Create PO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1483,7 +1479,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Process Payment</t>
+          <t>Approve Access</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1511,7 +1507,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Approve PO, Post JE</t>
+          <t>Approve Access, Approve PO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1534,12 +1530,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Create PO</t>
+          <t>Create Vendor, Approve Access, Approve JE</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1562,12 +1558,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Approve Access</t>
+          <t>Approve JE, Process Payment, Approve PO</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1590,12 +1586,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Approve JE</t>
+          <t>Approve PO, Create Vendor, Approve Access</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1618,12 +1614,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Approve Access</t>
+          <t>Post JE</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1646,12 +1642,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Maintain Access</t>
+          <t>Create Vendor</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1679,7 +1675,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Create PO, Process Payment</t>
+          <t>Post JE</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1702,12 +1698,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Approve JE</t>
+          <t>Maintain Access, Approve PO, Approve Access</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1730,12 +1726,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Post JE</t>
+          <t>Approve JE, Approve PO, Maintain Access</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1758,20 +1754,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Create Vendor, Create PO</t>
+          <t>Approve Access, Process Payment, Create Vendor</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>CC-564: Manager review of transactions</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Post JE, Process Payment, Maintain Access</t>
+          <t>Approve PO</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Approve PO</t>
+          <t>Approve Access, Approve PO, Maintain Access</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1842,24 +1842,20 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Create Vendor, Process Payment</t>
+          <t>Create PO</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>CC-669: Manager review of transactions</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1879,19 +1875,15 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Process Payment, Approve JE, Post JE</t>
+          <t>Approve Access, Create Vendor</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>CC-506: Manager review of transactions</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1906,12 +1898,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Approve JE, Process Payment</t>
+          <t>Maintain Access</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1934,12 +1926,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Approve JE, Process Payment</t>
+          <t>Approve JE, Maintain Access</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1962,12 +1954,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Create PO</t>
+          <t>Create PO, Process Payment</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1990,12 +1982,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Process Payment, Create PO, Create Vendor</t>
+          <t>Process Payment, Create Vendor, Post JE</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2005,7 +1997,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CC-665: Manager review of transactions</t>
+          <t>CC-235: Manager review of transactions</t>
         </is>
       </c>
     </row>
@@ -2022,12 +2014,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Approve JE, Maintain Access</t>
+          <t>Maintain Access</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2050,12 +2042,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Approve PO</t>
+          <t>Post JE, Maintain Access, Approve Access</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2078,24 +2070,20 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Process Payment, Create Vendor, Post JE</t>
+          <t>Approve PO</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>CC-433: Manager review of transactions</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2115,15 +2103,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Maintain Access</t>
+          <t>Approve JE, Post JE</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>CC-625: Manager review of transactions</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2138,12 +2130,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Create Vendor</t>
+          <t>Process Payment</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2166,12 +2158,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Approve JE, Maintain Access, Approve Access</t>
+          <t>Create PO, Approve Access, Maintain Access</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2194,12 +2186,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Create PO, Approve JE, Maintain Access</t>
+          <t>Approve JE, Maintain Access, Process Payment</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2222,12 +2214,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Create Vendor, Post JE, Approve PO</t>
+          <t>Create Vendor</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2250,12 +2242,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Post JE, Approve PO, Process Payment</t>
+          <t>Approve JE, Approve PO, Process Payment</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2278,20 +2270,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Create PO</t>
+          <t>Approve JE, Post JE, Maintain Access</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>CC-525: Manager review of transactions</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2306,12 +2302,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Process Payment, Create PO, Post JE</t>
+          <t>Post JE, Process Payment, Create PO</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2334,12 +2330,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Approve JE</t>
+          <t>Approve PO, Process Payment</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2362,12 +2358,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Approve JE</t>
+          <t>Create PO, Post JE, Process Payment</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2390,12 +2386,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Create PO, Approve Access</t>
+          <t>Process Payment, Approve JE, Create PO</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2418,12 +2414,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Create Vendor, Maintain Access, Create PO</t>
+          <t>Maintain Access</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2446,12 +2442,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Approve JE</t>
+          <t>Process Payment, Create PO, Post JE</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2474,12 +2470,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Approve PO, Create Vendor, Maintain Access</t>
+          <t>Create PO</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2507,7 +2503,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Create Vendor</t>
+          <t>Maintain Access, Approve PO</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2530,12 +2526,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Approve Access, Approve JE, Create Vendor</t>
+          <t>Process Payment, Approve Access, Post JE</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2563,15 +2559,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Approve JE, Approve PO, Approve Access</t>
+          <t>Create PO, Approve JE, Approve PO</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>CC-567: Manager review of transactions</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2586,24 +2586,20 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Post JE, Approve JE</t>
+          <t>Approve JE, Approve Access, Process Payment</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>CC-977: Manager review of transactions</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2618,20 +2614,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Create Vendor</t>
+          <t>Create Vendor, Process Payment</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>CC-677: Manager review of transactions</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Maintain Access, Approve Access, Post JE</t>
+          <t>Approve JE, Approve Access, Maintain Access</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Approve JE</t>
+          <t>Approve Access, Approve PO, Maintain Access</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Approve PO, Process Payment, Approve Access</t>
+          <t>Post JE, Approve PO, Create Vendor</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Approve PO, Approve Access, Create Vendor</t>
+          <t>Process Payment, Approve JE, Maintain Access</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Approve PO</t>
+          <t>Approve Access, Create Vendor</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2786,12 +2786,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Create PO, Create Vendor</t>
+          <t>Approve PO, Post JE</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Approve PO</t>
+          <t>Approve JE, Maintain Access</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Approve PO, Approve JE</t>
+          <t>Create PO, Create Vendor</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2870,12 +2870,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Maintain Access</t>
+          <t>Approve Access, Approve JE</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2898,12 +2898,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Maintain Access, Approve PO, Process Payment</t>
+          <t>Approve Access, Approve PO, Maintain Access</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Approve JE, Post JE</t>
+          <t>Post JE, Approve PO, Create PO</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>CC-382: Manager review of transactions</t>
+          <t>CC-159: Manager review of transactions</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Approve Access</t>
+          <t>Create PO</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Approve Access</t>
+          <t>Process Payment, Create PO, Maintain Access</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3014,12 +3014,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Post JE</t>
+          <t>Approve Access, Create PO</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3042,12 +3042,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Post JE, Create PO</t>
+          <t>Create Vendor</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3075,19 +3075,15 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Create Vendor, Process Payment</t>
+          <t>Approve Access, Process Payment, Approve JE</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>CC-632: Manager review of transactions</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3102,24 +3098,20 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Approve PO, Post JE, Create PO</t>
+          <t>Approve JE, Create Vendor</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>CC-569: Manager review of transactions</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3134,12 +3126,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Approve Access, Approve JE, Create PO</t>
+          <t>Process Payment</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3167,19 +3159,15 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Create Vendor, Post JE, Process Payment</t>
+          <t>Maintain Access</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>CC-994: Manager review of transactions</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3194,12 +3182,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Approve PO</t>
+          <t>Maintain Access</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3222,12 +3210,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Process Payment</t>
+          <t>Post JE</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3250,24 +3238,20 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Post JE, Approve JE, Create Vendor</t>
+          <t>Post JE</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>CC-112: Manager review of transactions</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3282,12 +3266,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Approve PO</t>
+          <t>Post JE, Process Payment</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3310,12 +3294,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Approve Access, Approve PO</t>
+          <t>Approve Access</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3338,12 +3322,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Create PO, Process Payment</t>
+          <t>Approve PO</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3366,12 +3350,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Approve Access, Approve PO</t>
+          <t>Approve Access</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3394,12 +3378,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Process Payment</t>
+          <t>Create Vendor, Create PO, Approve JE</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3422,12 +3406,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Post JE, Create PO, Process Payment</t>
+          <t>Process Payment, Approve PO</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3455,7 +3439,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Maintain Access, Process Payment</t>
+          <t>Approve JE, Create PO</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -3483,19 +3467,15 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Post JE, Create PO, Approve JE</t>
+          <t>Approve PO, Approve Access, Maintain Access</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>CC-905: Manager review of transactions</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3510,12 +3490,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Approve JE</t>
+          <t>Process Payment, Create PO</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3538,24 +3518,20 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Create Vendor, Process Payment</t>
+          <t>Process Payment, Approve Access</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>CC-817: Manager review of transactions</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3570,12 +3546,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Approve Access, Process Payment</t>
+          <t>Post JE, Approve Access</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3598,12 +3574,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Post JE</t>
+          <t>Approve JE, Approve Access</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3626,7 +3602,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3654,12 +3630,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Approve JE, Maintain Access, Post JE</t>
+          <t>Create Vendor, Process Payment</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -3669,7 +3645,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CC-738: Manager review of transactions</t>
+          <t>CC-672: Manager review of transactions</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3662,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Process Payment, Post JE, Create PO</t>
+          <t>Approve PO, Approve JE, Create Vendor</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -3719,19 +3695,15 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Maintain Access, Post JE, Approve JE</t>
+          <t>Process Payment, Approve PO, Maintain Access</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>CC-701: Manager review of transactions</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3746,24 +3718,20 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Process Payment, Approve Access, Create Vendor</t>
+          <t>Approve Access</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>CC-635: Manager review of transactions</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3783,7 +3751,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Create PO, Post JE</t>
+          <t>Approve Access, Maintain Access</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -3806,12 +3774,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Approve Access</t>
+          <t>Approve PO</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -3834,20 +3802,24 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Process Payment</t>
+          <t>Approve JE, Create PO, Post JE</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>CC-573: Manager review of transactions</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3862,12 +3834,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Create PO</t>
+          <t>Process Payment</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -3890,12 +3862,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Maintain Access</t>
+          <t>Approve JE</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -3918,12 +3890,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Create Vendor, Maintain Access, Post JE</t>
+          <t>Process Payment</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -3962,7 +3934,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
     </row>
